--- a/property_management_forms/035_property_asset_monitoring_registration_form--property_management_forms.xlsx
+++ b/property_management_forms/035_property_asset_monitoring_registration_form--property_management_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'asset_type_1'}</t>
+          <t>asset_type_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'asset_type_1'}</t>
+          <t>asset type 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'asset_type_2'}</t>
+          <t>asset_type_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'asset_type_2'}</t>
+          <t>asset type 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'asset_model_1'}</t>
+          <t>asset_model_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'asset_model_1'}</t>
+          <t>asset model 1</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'asset_model_2'}</t>
+          <t>asset_model_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'asset_model_2'}</t>
+          <t>asset model 2</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'asset_model_3'}</t>
+          <t>asset_model_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'asset_model_3'}</t>
+          <t>asset model 3</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'in_service'}</t>
+          <t>in_service</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'In Service'}</t>
+          <t>In Service</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'out_of_service'}</t>
+          <t>out_of_service</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Out of Service'}</t>
+          <t>Out of Service</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'maintenance'}</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Maintenance'}</t>
+          <t>Maintenance</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'category_1'}</t>
+          <t>category_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Category 1'}</t>
+          <t>Category 1</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'category_2'}</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Category 2'}</t>
+          <t>Category 2</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'category_3'}</t>
+          <t>category_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Category 3'}</t>
+          <t>Category 3</t>
         </is>
       </c>
     </row>
